--- a/python/output/INTEREST_PAYMENTS.xlsx
+++ b/python/output/INTEREST_PAYMENTS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D554"/>
+  <dimension ref="A1:D712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9139,6 +9139,2476 @@
         <v>15.5309444318181</v>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" s="1" t="n">
+        <v>1859</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D555" t="n">
+        <v>18.3701078150735</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="n">
+        <v>1863</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D556" t="n">
+        <v>0.340713650725389</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="n">
+        <v>1864</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D557" t="n">
+        <v>7.83661389642186</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="n">
+        <v>1868</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D558" t="n">
+        <v>3.20656117385791</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="n">
+        <v>1869</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D559" t="n">
+        <v>2.492931518597</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D560" t="n">
+        <v>3.92717142468875</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="n">
+        <v>1875</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D561" t="n">
+        <v>20.8277384040526</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="n">
+        <v>1876</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D562" t="n">
+        <v>1.32773869899373</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="n">
+        <v>1880</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D563" t="n">
+        <v>4.77840242256855</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="n">
+        <v>1884</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D564" t="n">
+        <v>27.0987532818901</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="n">
+        <v>1886</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="n">
+        <v>1890</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D566" t="n">
+        <v>4.97666661384632</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="n">
+        <v>1892</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D567" t="n">
+        <v>0.590221176255857</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="n">
+        <v>1894</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D568" t="n">
+        <v>3.54372318434982</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="n">
+        <v>1895</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D569" t="n">
+        <v>3.4419404251668</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="n">
+        <v>1896</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D570" t="n">
+        <v>14.8113398704174</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="n">
+        <v>1897</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D571" t="n">
+        <v>6.82374829265213</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="n">
+        <v>1898</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D572" t="n">
+        <v>0.557011168639761</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D573" t="n">
+        <v>13.0049373856116</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D574" t="n">
+        <v>16.0641742418659</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>1908</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D575" t="n">
+        <v>4.19429528548204</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>1909</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D576" t="n">
+        <v>1.98134992760279</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>1910</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D577" t="n">
+        <v>0.968275088782061</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>1913</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D578" t="n">
+        <v>1.00172958419483</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>1922</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D580" t="n">
+        <v>5.94138552560565</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>1926</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D581" t="n">
+        <v>0.193791860741849</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>1929</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D582" t="n">
+        <v>1.22108861706105</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>1931</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D583" t="n">
+        <v>3.07679448440757</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>1935</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D584" t="n">
+        <v>7.90342486310386</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D585" t="n">
+        <v>5.68511614568397</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>1950</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>1953</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D587" t="n">
+        <v>4.45653656154736</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>1955</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D588" t="n">
+        <v>6.06278465909743</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>1960</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>1963</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>1965</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D591" t="n">
+        <v>3.39904474407162</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>1968</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>ISL</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D592" t="n">
+        <v>12.3594773915544</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>1969</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D593" t="n">
+        <v>8.20472787897771</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>1970</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D594" t="n">
+        <v>8.44624035121257</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>1972</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D595" t="n">
+        <v>17.2660064885933</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>1973</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>1974</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D597" t="n">
+        <v>8.892017182465271</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>1977</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D598" t="n">
+        <v>1.85235096785957</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>1980</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D599" t="n">
+        <v>3.32515319325515</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>LAO</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D600" t="n">
+        <v>7.98466903332311</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D601" t="n">
+        <v>1.45038323548598</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D602" t="n">
+        <v>0.346141216711818</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D603" t="n">
+        <v>1.57991817714356</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D604" t="n">
+        <v>8.732232723526201</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D605" t="n">
+        <v>15.8259382639258</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>MLT</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D606" t="n">
+        <v>3.1794775770059</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D608" t="n">
+        <v>16.2860332189783</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D610" t="n">
+        <v>1.38065388084474</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D611" t="n">
+        <v>0.391633770502513</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D612" t="n">
+        <v>2.78400361370464</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D614" t="n">
+        <v>6.55420064925363</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D615" t="n">
+        <v>14.289552421245</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D616" t="n">
+        <v>2.92109045364879</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D617" t="n">
+        <v>6.00580997592147</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="n">
+        <v>2055</v>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D618" t="n">
+        <v>4.70535049017556</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="n">
+        <v>2059</v>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D620" t="n">
+        <v>2.83627486303424</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="n">
+        <v>2061</v>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D621" t="n">
+        <v>9.506167012026401</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="n">
+        <v>2062</v>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D622" t="n">
+        <v>0.348080818137311</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="n">
+        <v>2073</v>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="n">
+        <v>2075</v>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D624" t="n">
+        <v>2.94219268473397</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="n">
+        <v>2076</v>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D625" t="n">
+        <v>2.83511674514534</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="n">
+        <v>2077</v>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D626" t="n">
+        <v>0.599603850816015</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="n">
+        <v>2087</v>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D627" t="n">
+        <v>6.3896779659607</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="n">
+        <v>2097</v>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="n">
+        <v>2098</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D629" t="n">
+        <v>9.853825184240989</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="n">
+        <v>2102</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D630" t="n">
+        <v>9.265518484774651</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="n">
+        <v>2105</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D631" t="n">
+        <v>11.3815152236966</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="n">
+        <v>2111</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="n">
+        <v>2117</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D633" t="n">
+        <v>14.8790215377287</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="n">
+        <v>2124</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>AGO</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D634" t="n">
+        <v>12.9570213148472</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="n">
+        <v>2128</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>ARE</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D635" t="n">
+        <v>1.1786818753689</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="n">
+        <v>2129</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D636" t="n">
+        <v>9.47430226617865</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="n">
+        <v>2133</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>AUS</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D637" t="n">
+        <v>3.08204640033961</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="n">
+        <v>2134</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>AUT</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D638" t="n">
+        <v>2.15569416078849</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="n">
+        <v>2137</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D639" t="n">
+        <v>3.41746566567103</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="n">
+        <v>2140</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>BGD</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="n">
+        <v>2141</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>BGR</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D641" t="n">
+        <v>1.00156799662028</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="n">
+        <v>2145</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D642" t="n">
+        <v>3.26481540545399</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="n">
+        <v>2149</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D643" t="n">
+        <v>28.8867766914126</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="n">
+        <v>2151</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>BRN</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="n">
+        <v>2155</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D645" t="n">
+        <v>5.79267225578024</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n">
+        <v>2157</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D646" t="n">
+        <v>0.676569274072201</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n">
+        <v>2159</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D647" t="n">
+        <v>3.81839448820788</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n">
+        <v>2160</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>CHN</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="n">
+        <v>2161</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>CIV</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D649" t="n">
+        <v>17.4439105528207</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="n">
+        <v>2162</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n">
+        <v>2163</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D651" t="n">
+        <v>0.514036894677786</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n">
+        <v>2165</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D652" t="n">
+        <v>15.4743411391649</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="n">
+        <v>2168</v>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>CRI</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D653" t="n">
+        <v>15.2927261286011</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n">
+        <v>2173</v>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>CYP</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D654" t="n">
+        <v>3.26446209486234</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="n">
+        <v>2174</v>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>CZE</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D655" t="n">
+        <v>2.95765461223435</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="n">
+        <v>2175</v>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>DEU</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D656" t="n">
+        <v>1.45773373315771</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n">
+        <v>2178</v>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>DNK</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D657" t="n">
+        <v>1.61289210854626</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="n">
+        <v>2187</v>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>EGY</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="n">
+        <v>2190</v>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>ESP</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D659" t="n">
+        <v>6.44093611786415</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="n">
+        <v>2191</v>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D660" t="n">
+        <v>0.298905511398114</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="n">
+        <v>2194</v>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>FIN</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D661" t="n">
+        <v>1.30450765516488</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="n">
+        <v>2196</v>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D662" t="n">
+        <v>4.15502068013923</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D663" t="n">
+        <v>11.8284417545897</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="n">
+        <v>2208</v>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D664" t="n">
+        <v>5.44514784838529</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="n">
+        <v>2215</v>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="n">
+        <v>2218</v>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>HRV</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D666" t="n">
+        <v>3.84002783469285</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="n">
+        <v>2220</v>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>HUN</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D667" t="n">
+        <v>7.11584976596727</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>2225</v>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>2228</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D669" t="n">
+        <v>33.9761997637185</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>2230</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>IRL</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D670" t="n">
+        <v>2.95593677862342</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>2233</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>ISL</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D671" t="n">
+        <v>16.3468153902564</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
+        <v>2234</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>ISR</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D672" t="n">
+        <v>9.73112216641699</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>2235</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D673" t="n">
+        <v>10.1438772928371</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
+        <v>2237</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>JOR</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D674" t="n">
+        <v>16.0152568992596</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
+        <v>2238</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>JPN</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
+        <v>2239</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>KAZ</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D676" t="n">
+        <v>7.06990907348092</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
+        <v>2242</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>KHM</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D677" t="n">
+        <v>1.65950112644265</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n">
+        <v>2245</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>KOR</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D678" t="n">
+        <v>3.5979328479696</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n">
+        <v>2248</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>LAO</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D679" t="n">
+        <v>11.8499360825446</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>2262</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>LTU</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D680" t="n">
+        <v>1.00470685204867</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
+        <v>2263</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>LUX</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D681" t="n">
+        <v>0.345531988873435</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n">
+        <v>2264</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>LVA</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D682" t="n">
+        <v>1.46175456089919</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n">
+        <v>2267</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D683" t="n">
+        <v>7.96111730498483</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>2273</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D684" t="n">
+        <v>17.1966048280522</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
+        <v>2278</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>MLT</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D685" t="n">
+        <v>2.8480038315487</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
+        <v>2279</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>MMR</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>2288</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>MYS</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D687" t="n">
+        <v>14.020107638443</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>2293</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n">
+        <v>2295</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>NLD</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D689" t="n">
+        <v>1.30958937641515</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n">
+        <v>2296</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>NOR</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D690" t="n">
+        <v>0.456615208184397</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n">
+        <v>2299</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>NZL</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D691" t="n">
+        <v>3.2038226492858</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="n">
+        <v>2303</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>PAK</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="n">
+        <v>2305</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="n">
+        <v>2306</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D694" t="n">
+        <v>14.1895600248204</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="n">
+        <v>2309</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D695" t="n">
+        <v>4.05151988034782</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="n">
+        <v>2313</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>PRT</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D696" t="n">
+        <v>4.95387039532298</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="n">
+        <v>2320</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D697" t="n">
+        <v>4.52784666028597</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
+        <v>2321</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>RUS</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>2324</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>SAU</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D699" t="n">
+        <v>2.39041526354088</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>2326</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D700" t="n">
+        <v>9.86295387445667</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>2327</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>SGP</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D701" t="n">
+        <v>0.423379410650531</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>2338</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>STP</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="n">
+        <v>2340</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>SVK</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D703" t="n">
+        <v>2.69872629068166</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="n">
+        <v>2341</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>SVN</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D704" t="n">
+        <v>2.6268832941425</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="n">
+        <v>2342</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D705" t="n">
+        <v>1.29388501735187</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="n">
+        <v>2352</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>THA</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D706" t="n">
+        <v>6.75505455085063</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="n">
+        <v>2362</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>TUN</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="n">
+        <v>2363</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D708" t="n">
+        <v>15.4826696359583</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="n">
+        <v>2367</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>UKR</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D709" t="n">
+        <v>7.25891657503026</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="n">
+        <v>2370</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D710" t="n">
+        <v>13.418892172087</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="n">
+        <v>2376</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="n">
+        <v>2382</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D712" t="n">
+        <v>15.9129870924546</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/python/output/INTEREST_PAYMENTS.xlsx
+++ b/python/output/INTEREST_PAYMENTS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D712"/>
+  <dimension ref="A1:D554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9139,2476 +9139,6 @@
         <v>15.5309444318181</v>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" s="1" t="n">
-        <v>1859</v>
-      </c>
-      <c r="B555" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="C555" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D555" t="n">
-        <v>18.3701078150735</v>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" s="1" t="n">
-        <v>1863</v>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>ARE</t>
-        </is>
-      </c>
-      <c r="C556" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D556" t="n">
-        <v>0.340713650725389</v>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" s="1" t="n">
-        <v>1864</v>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>ARG</t>
-        </is>
-      </c>
-      <c r="C557" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D557" t="n">
-        <v>7.83661389642186</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" s="1" t="n">
-        <v>1868</v>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="C558" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D558" t="n">
-        <v>3.20656117385791</v>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" s="1" t="n">
-        <v>1869</v>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>AUT</t>
-        </is>
-      </c>
-      <c r="C559" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D559" t="n">
-        <v>2.492931518597</v>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" s="1" t="n">
-        <v>1872</v>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="C560" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D560" t="n">
-        <v>3.92717142468875</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" s="1" t="n">
-        <v>1875</v>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>BGD</t>
-        </is>
-      </c>
-      <c r="C561" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D561" t="n">
-        <v>20.8277384040526</v>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" s="1" t="n">
-        <v>1876</v>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>BGR</t>
-        </is>
-      </c>
-      <c r="C562" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D562" t="n">
-        <v>1.32773869899373</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" s="1" t="n">
-        <v>1880</v>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>BLR</t>
-        </is>
-      </c>
-      <c r="C563" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D563" t="n">
-        <v>4.77840242256855</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" s="1" t="n">
-        <v>1884</v>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="C564" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D564" t="n">
-        <v>27.0987532818901</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" s="1" t="n">
-        <v>1886</v>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>BRN</t>
-        </is>
-      </c>
-      <c r="C565" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D565" t="inlineStr"/>
-    </row>
-    <row r="566">
-      <c r="A566" s="1" t="n">
-        <v>1890</v>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="C566" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D566" t="n">
-        <v>4.97666661384632</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" s="1" t="n">
-        <v>1892</v>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>CHE</t>
-        </is>
-      </c>
-      <c r="C567" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D567" t="n">
-        <v>0.590221176255857</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" s="1" t="n">
-        <v>1894</v>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>CHL</t>
-        </is>
-      </c>
-      <c r="C568" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D568" t="n">
-        <v>3.54372318434982</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" s="1" t="n">
-        <v>1895</v>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>CHN</t>
-        </is>
-      </c>
-      <c r="C569" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D569" t="n">
-        <v>3.4419404251668</v>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" s="1" t="n">
-        <v>1896</v>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>CIV</t>
-        </is>
-      </c>
-      <c r="C570" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D570" t="n">
-        <v>14.8113398704174</v>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" s="1" t="n">
-        <v>1897</v>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>CMR</t>
-        </is>
-      </c>
-      <c r="C571" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D571" t="n">
-        <v>6.82374829265213</v>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" s="1" t="n">
-        <v>1898</v>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="C572" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D572" t="n">
-        <v>0.557011168639761</v>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="C573" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D573" t="n">
-        <v>13.0049373856116</v>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" s="1" t="n">
-        <v>1903</v>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>CRI</t>
-        </is>
-      </c>
-      <c r="C574" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D574" t="n">
-        <v>16.0641742418659</v>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" s="1" t="n">
-        <v>1908</v>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>CYP</t>
-        </is>
-      </c>
-      <c r="C575" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D575" t="n">
-        <v>4.19429528548204</v>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" s="1" t="n">
-        <v>1909</v>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>CZE</t>
-        </is>
-      </c>
-      <c r="C576" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D576" t="n">
-        <v>1.98134992760279</v>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" s="1" t="n">
-        <v>1910</v>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>DEU</t>
-        </is>
-      </c>
-      <c r="C577" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D577" t="n">
-        <v>0.968275088782061</v>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" s="1" t="n">
-        <v>1913</v>
-      </c>
-      <c r="B578" t="inlineStr">
-        <is>
-          <t>DNK</t>
-        </is>
-      </c>
-      <c r="C578" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D578" t="n">
-        <v>1.00172958419483</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" s="1" t="n">
-        <v>1922</v>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t>EGY</t>
-        </is>
-      </c>
-      <c r="C579" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D579" t="inlineStr"/>
-    </row>
-    <row r="580">
-      <c r="A580" s="1" t="n">
-        <v>1925</v>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>ESP</t>
-        </is>
-      </c>
-      <c r="C580" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D580" t="n">
-        <v>5.94138552560565</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" s="1" t="n">
-        <v>1926</v>
-      </c>
-      <c r="B581" t="inlineStr">
-        <is>
-          <t>EST</t>
-        </is>
-      </c>
-      <c r="C581" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D581" t="n">
-        <v>0.193791860741849</v>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" s="1" t="n">
-        <v>1929</v>
-      </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="C582" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D582" t="n">
-        <v>1.22108861706105</v>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" s="1" t="n">
-        <v>1931</v>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="C583" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D583" t="n">
-        <v>3.07679448440757</v>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" s="1" t="n">
-        <v>1935</v>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>GBR</t>
-        </is>
-      </c>
-      <c r="C584" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D584" t="n">
-        <v>7.90342486310386</v>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" s="1" t="n">
-        <v>1943</v>
-      </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t>GRC</t>
-        </is>
-      </c>
-      <c r="C585" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D585" t="n">
-        <v>5.68511614568397</v>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" s="1" t="n">
-        <v>1950</v>
-      </c>
-      <c r="B586" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="C586" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D586" t="inlineStr"/>
-    </row>
-    <row r="587">
-      <c r="A587" s="1" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>HRV</t>
-        </is>
-      </c>
-      <c r="C587" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D587" t="n">
-        <v>4.45653656154736</v>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" s="1" t="n">
-        <v>1955</v>
-      </c>
-      <c r="B588" t="inlineStr">
-        <is>
-          <t>HUN</t>
-        </is>
-      </c>
-      <c r="C588" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D588" t="n">
-        <v>6.06278465909743</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" s="1" t="n">
-        <v>1960</v>
-      </c>
-      <c r="B589" t="inlineStr">
-        <is>
-          <t>IDN</t>
-        </is>
-      </c>
-      <c r="C589" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D589" t="inlineStr"/>
-    </row>
-    <row r="590">
-      <c r="A590" s="1" t="n">
-        <v>1963</v>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="C590" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D590" t="inlineStr"/>
-    </row>
-    <row r="591">
-      <c r="A591" s="1" t="n">
-        <v>1965</v>
-      </c>
-      <c r="B591" t="inlineStr">
-        <is>
-          <t>IRL</t>
-        </is>
-      </c>
-      <c r="C591" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D591" t="n">
-        <v>3.39904474407162</v>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" s="1" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B592" t="inlineStr">
-        <is>
-          <t>ISL</t>
-        </is>
-      </c>
-      <c r="C592" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D592" t="n">
-        <v>12.3594773915544</v>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" s="1" t="n">
-        <v>1969</v>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
-      <c r="C593" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D593" t="n">
-        <v>8.20472787897771</v>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" s="1" t="n">
-        <v>1970</v>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="C594" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D594" t="n">
-        <v>8.44624035121257</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" s="1" t="n">
-        <v>1972</v>
-      </c>
-      <c r="B595" t="inlineStr">
-        <is>
-          <t>JOR</t>
-        </is>
-      </c>
-      <c r="C595" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D595" t="n">
-        <v>17.2660064885933</v>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" s="1" t="n">
-        <v>1973</v>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>JPN</t>
-        </is>
-      </c>
-      <c r="C596" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D596" t="inlineStr"/>
-    </row>
-    <row r="597">
-      <c r="A597" s="1" t="n">
-        <v>1974</v>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t>KAZ</t>
-        </is>
-      </c>
-      <c r="C597" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D597" t="n">
-        <v>8.892017182465271</v>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" s="1" t="n">
-        <v>1977</v>
-      </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>KHM</t>
-        </is>
-      </c>
-      <c r="C598" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D598" t="n">
-        <v>1.85235096785957</v>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" s="1" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B599" t="inlineStr">
-        <is>
-          <t>KOR</t>
-        </is>
-      </c>
-      <c r="C599" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D599" t="n">
-        <v>3.32515319325515</v>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" s="1" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t>LAO</t>
-        </is>
-      </c>
-      <c r="C600" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D600" t="n">
-        <v>7.98466903332311</v>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" s="1" t="n">
-        <v>1997</v>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>LTU</t>
-        </is>
-      </c>
-      <c r="C601" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D601" t="n">
-        <v>1.45038323548598</v>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" s="1" t="n">
-        <v>1998</v>
-      </c>
-      <c r="B602" t="inlineStr">
-        <is>
-          <t>LUX</t>
-        </is>
-      </c>
-      <c r="C602" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D602" t="n">
-        <v>0.346141216711818</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" s="1" t="n">
-        <v>1999</v>
-      </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>LVA</t>
-        </is>
-      </c>
-      <c r="C603" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D603" t="n">
-        <v>1.57991817714356</v>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" s="1" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B604" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="C604" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D604" t="n">
-        <v>8.732232723526201</v>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" s="1" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>MEX</t>
-        </is>
-      </c>
-      <c r="C605" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D605" t="n">
-        <v>15.8259382639258</v>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" s="1" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B606" t="inlineStr">
-        <is>
-          <t>MLT</t>
-        </is>
-      </c>
-      <c r="C606" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D606" t="n">
-        <v>3.1794775770059</v>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" s="1" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B607" t="inlineStr">
-        <is>
-          <t>MMR</t>
-        </is>
-      </c>
-      <c r="C607" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D607" t="inlineStr"/>
-    </row>
-    <row r="608">
-      <c r="A608" s="1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B608" t="inlineStr">
-        <is>
-          <t>MYS</t>
-        </is>
-      </c>
-      <c r="C608" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D608" t="n">
-        <v>16.2860332189783</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B609" t="inlineStr">
-        <is>
-          <t>NGA</t>
-        </is>
-      </c>
-      <c r="C609" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D609" t="inlineStr"/>
-    </row>
-    <row r="610">
-      <c r="A610" s="1" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B610" t="inlineStr">
-        <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="C610" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D610" t="n">
-        <v>1.38065388084474</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" s="1" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>NOR</t>
-        </is>
-      </c>
-      <c r="C611" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D611" t="n">
-        <v>0.391633770502513</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" s="1" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B612" t="inlineStr">
-        <is>
-          <t>NZL</t>
-        </is>
-      </c>
-      <c r="C612" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D612" t="n">
-        <v>2.78400361370464</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" s="1" t="n">
-        <v>2038</v>
-      </c>
-      <c r="B613" t="inlineStr">
-        <is>
-          <t>PAK</t>
-        </is>
-      </c>
-      <c r="C613" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D613" t="inlineStr"/>
-    </row>
-    <row r="614">
-      <c r="A614" s="1" t="n">
-        <v>2040</v>
-      </c>
-      <c r="B614" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="C614" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D614" t="n">
-        <v>6.55420064925363</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" s="1" t="n">
-        <v>2041</v>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>PHL</t>
-        </is>
-      </c>
-      <c r="C615" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D615" t="n">
-        <v>14.289552421245</v>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" s="1" t="n">
-        <v>2044</v>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>POL</t>
-        </is>
-      </c>
-      <c r="C616" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D616" t="n">
-        <v>2.92109045364879</v>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" s="1" t="n">
-        <v>2048</v>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>PRT</t>
-        </is>
-      </c>
-      <c r="C617" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D617" t="n">
-        <v>6.00580997592147</v>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" s="1" t="n">
-        <v>2055</v>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>ROU</t>
-        </is>
-      </c>
-      <c r="C618" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D618" t="n">
-        <v>4.70535049017556</v>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" s="1" t="n">
-        <v>2056</v>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>RUS</t>
-        </is>
-      </c>
-      <c r="C619" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D619" t="inlineStr"/>
-    </row>
-    <row r="620">
-      <c r="A620" s="1" t="n">
-        <v>2059</v>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>SAU</t>
-        </is>
-      </c>
-      <c r="C620" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D620" t="n">
-        <v>2.83627486303424</v>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" s="1" t="n">
-        <v>2061</v>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>SEN</t>
-        </is>
-      </c>
-      <c r="C621" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D621" t="n">
-        <v>9.506167012026401</v>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" s="1" t="n">
-        <v>2062</v>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-      <c r="C622" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D622" t="n">
-        <v>0.348080818137311</v>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" s="1" t="n">
-        <v>2073</v>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>STP</t>
-        </is>
-      </c>
-      <c r="C623" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D623" t="inlineStr"/>
-    </row>
-    <row r="624">
-      <c r="A624" s="1" t="n">
-        <v>2075</v>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>SVK</t>
-        </is>
-      </c>
-      <c r="C624" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D624" t="n">
-        <v>2.94219268473397</v>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" s="1" t="n">
-        <v>2076</v>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>SVN</t>
-        </is>
-      </c>
-      <c r="C625" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D625" t="n">
-        <v>2.83511674514534</v>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" s="1" t="n">
-        <v>2077</v>
-      </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>SWE</t>
-        </is>
-      </c>
-      <c r="C626" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D626" t="n">
-        <v>0.599603850816015</v>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" s="1" t="n">
-        <v>2087</v>
-      </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="C627" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D627" t="n">
-        <v>6.3896779659607</v>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" s="1" t="n">
-        <v>2097</v>
-      </c>
-      <c r="B628" t="inlineStr">
-        <is>
-          <t>TUN</t>
-        </is>
-      </c>
-      <c r="C628" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D628" t="inlineStr"/>
-    </row>
-    <row r="629">
-      <c r="A629" s="1" t="n">
-        <v>2098</v>
-      </c>
-      <c r="B629" t="inlineStr">
-        <is>
-          <t>TUR</t>
-        </is>
-      </c>
-      <c r="C629" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D629" t="n">
-        <v>9.853825184240989</v>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" s="1" t="n">
-        <v>2102</v>
-      </c>
-      <c r="B630" t="inlineStr">
-        <is>
-          <t>UKR</t>
-        </is>
-      </c>
-      <c r="C630" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D630" t="n">
-        <v>9.265518484774651</v>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" s="1" t="n">
-        <v>2105</v>
-      </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C631" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D631" t="n">
-        <v>11.3815152236966</v>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" s="1" t="n">
-        <v>2111</v>
-      </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>VNM</t>
-        </is>
-      </c>
-      <c r="C632" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D632" t="inlineStr"/>
-    </row>
-    <row r="633">
-      <c r="A633" s="1" t="n">
-        <v>2117</v>
-      </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>ZAF</t>
-        </is>
-      </c>
-      <c r="C633" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D633" t="n">
-        <v>14.8790215377287</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" s="1" t="n">
-        <v>2124</v>
-      </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>AGO</t>
-        </is>
-      </c>
-      <c r="C634" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D634" t="n">
-        <v>12.9570213148472</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" s="1" t="n">
-        <v>2128</v>
-      </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>ARE</t>
-        </is>
-      </c>
-      <c r="C635" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D635" t="n">
-        <v>1.1786818753689</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" s="1" t="n">
-        <v>2129</v>
-      </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>ARG</t>
-        </is>
-      </c>
-      <c r="C636" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D636" t="n">
-        <v>9.47430226617865</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" s="1" t="n">
-        <v>2133</v>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>AUS</t>
-        </is>
-      </c>
-      <c r="C637" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D637" t="n">
-        <v>3.08204640033961</v>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" s="1" t="n">
-        <v>2134</v>
-      </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>AUT</t>
-        </is>
-      </c>
-      <c r="C638" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D638" t="n">
-        <v>2.15569416078849</v>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" s="1" t="n">
-        <v>2137</v>
-      </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="C639" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D639" t="n">
-        <v>3.41746566567103</v>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" s="1" t="n">
-        <v>2140</v>
-      </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>BGD</t>
-        </is>
-      </c>
-      <c r="C640" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D640" t="inlineStr"/>
-    </row>
-    <row r="641">
-      <c r="A641" s="1" t="n">
-        <v>2141</v>
-      </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>BGR</t>
-        </is>
-      </c>
-      <c r="C641" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D641" t="n">
-        <v>1.00156799662028</v>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" s="1" t="n">
-        <v>2145</v>
-      </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>BLR</t>
-        </is>
-      </c>
-      <c r="C642" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D642" t="n">
-        <v>3.26481540545399</v>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" s="1" t="n">
-        <v>2149</v>
-      </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="C643" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D643" t="n">
-        <v>28.8867766914126</v>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" s="1" t="n">
-        <v>2151</v>
-      </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>BRN</t>
-        </is>
-      </c>
-      <c r="C644" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D644" t="inlineStr"/>
-    </row>
-    <row r="645">
-      <c r="A645" s="1" t="n">
-        <v>2155</v>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
-      <c r="C645" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D645" t="n">
-        <v>5.79267225578024</v>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" s="1" t="n">
-        <v>2157</v>
-      </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>CHE</t>
-        </is>
-      </c>
-      <c r="C646" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D646" t="n">
-        <v>0.676569274072201</v>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" s="1" t="n">
-        <v>2159</v>
-      </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>CHL</t>
-        </is>
-      </c>
-      <c r="C647" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D647" t="n">
-        <v>3.81839448820788</v>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" s="1" t="n">
-        <v>2160</v>
-      </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>CHN</t>
-        </is>
-      </c>
-      <c r="C648" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D648" t="inlineStr"/>
-    </row>
-    <row r="649">
-      <c r="A649" s="1" t="n">
-        <v>2161</v>
-      </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>CIV</t>
-        </is>
-      </c>
-      <c r="C649" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D649" t="n">
-        <v>17.4439105528207</v>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" s="1" t="n">
-        <v>2162</v>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>CMR</t>
-        </is>
-      </c>
-      <c r="C650" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D650" t="inlineStr"/>
-    </row>
-    <row r="651">
-      <c r="A651" s="1" t="n">
-        <v>2163</v>
-      </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>COD</t>
-        </is>
-      </c>
-      <c r="C651" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D651" t="n">
-        <v>0.514036894677786</v>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" s="1" t="n">
-        <v>2165</v>
-      </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="C652" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D652" t="n">
-        <v>15.4743411391649</v>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" s="1" t="n">
-        <v>2168</v>
-      </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>CRI</t>
-        </is>
-      </c>
-      <c r="C653" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D653" t="n">
-        <v>15.2927261286011</v>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" s="1" t="n">
-        <v>2173</v>
-      </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>CYP</t>
-        </is>
-      </c>
-      <c r="C654" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D654" t="n">
-        <v>3.26446209486234</v>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" s="1" t="n">
-        <v>2174</v>
-      </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>CZE</t>
-        </is>
-      </c>
-      <c r="C655" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D655" t="n">
-        <v>2.95765461223435</v>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" s="1" t="n">
-        <v>2175</v>
-      </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>DEU</t>
-        </is>
-      </c>
-      <c r="C656" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D656" t="n">
-        <v>1.45773373315771</v>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" s="1" t="n">
-        <v>2178</v>
-      </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>DNK</t>
-        </is>
-      </c>
-      <c r="C657" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D657" t="n">
-        <v>1.61289210854626</v>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" s="1" t="n">
-        <v>2187</v>
-      </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>EGY</t>
-        </is>
-      </c>
-      <c r="C658" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D658" t="inlineStr"/>
-    </row>
-    <row r="659">
-      <c r="A659" s="1" t="n">
-        <v>2190</v>
-      </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>ESP</t>
-        </is>
-      </c>
-      <c r="C659" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D659" t="n">
-        <v>6.44093611786415</v>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" s="1" t="n">
-        <v>2191</v>
-      </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>EST</t>
-        </is>
-      </c>
-      <c r="C660" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D660" t="n">
-        <v>0.298905511398114</v>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" s="1" t="n">
-        <v>2194</v>
-      </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>FIN</t>
-        </is>
-      </c>
-      <c r="C661" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D661" t="n">
-        <v>1.30450765516488</v>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" s="1" t="n">
-        <v>2196</v>
-      </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="C662" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D662" t="n">
-        <v>4.15502068013923</v>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" s="1" t="n">
-        <v>2200</v>
-      </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>GBR</t>
-        </is>
-      </c>
-      <c r="C663" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D663" t="n">
-        <v>11.8284417545897</v>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" s="1" t="n">
-        <v>2208</v>
-      </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>GRC</t>
-        </is>
-      </c>
-      <c r="C664" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D664" t="n">
-        <v>5.44514784838529</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" s="1" t="n">
-        <v>2215</v>
-      </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="C665" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D665" t="inlineStr"/>
-    </row>
-    <row r="666">
-      <c r="A666" s="1" t="n">
-        <v>2218</v>
-      </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>HRV</t>
-        </is>
-      </c>
-      <c r="C666" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D666" t="n">
-        <v>3.84002783469285</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" s="1" t="n">
-        <v>2220</v>
-      </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>HUN</t>
-        </is>
-      </c>
-      <c r="C667" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D667" t="n">
-        <v>7.11584976596727</v>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" s="1" t="n">
-        <v>2225</v>
-      </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>IDN</t>
-        </is>
-      </c>
-      <c r="C668" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D668" t="inlineStr"/>
-    </row>
-    <row r="669">
-      <c r="A669" s="1" t="n">
-        <v>2228</v>
-      </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="C669" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D669" t="n">
-        <v>33.9761997637185</v>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" s="1" t="n">
-        <v>2230</v>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>IRL</t>
-        </is>
-      </c>
-      <c r="C670" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D670" t="n">
-        <v>2.95593677862342</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" s="1" t="n">
-        <v>2233</v>
-      </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>ISL</t>
-        </is>
-      </c>
-      <c r="C671" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D671" t="n">
-        <v>16.3468153902564</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" s="1" t="n">
-        <v>2234</v>
-      </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>ISR</t>
-        </is>
-      </c>
-      <c r="C672" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D672" t="n">
-        <v>9.73112216641699</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" s="1" t="n">
-        <v>2235</v>
-      </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="C673" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D673" t="n">
-        <v>10.1438772928371</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" s="1" t="n">
-        <v>2237</v>
-      </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>JOR</t>
-        </is>
-      </c>
-      <c r="C674" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D674" t="n">
-        <v>16.0152568992596</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" s="1" t="n">
-        <v>2238</v>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>JPN</t>
-        </is>
-      </c>
-      <c r="C675" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D675" t="inlineStr"/>
-    </row>
-    <row r="676">
-      <c r="A676" s="1" t="n">
-        <v>2239</v>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>KAZ</t>
-        </is>
-      </c>
-      <c r="C676" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D676" t="n">
-        <v>7.06990907348092</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" s="1" t="n">
-        <v>2242</v>
-      </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>KHM</t>
-        </is>
-      </c>
-      <c r="C677" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D677" t="n">
-        <v>1.65950112644265</v>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" s="1" t="n">
-        <v>2245</v>
-      </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>KOR</t>
-        </is>
-      </c>
-      <c r="C678" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D678" t="n">
-        <v>3.5979328479696</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" s="1" t="n">
-        <v>2248</v>
-      </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>LAO</t>
-        </is>
-      </c>
-      <c r="C679" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D679" t="n">
-        <v>11.8499360825446</v>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" s="1" t="n">
-        <v>2262</v>
-      </c>
-      <c r="B680" t="inlineStr">
-        <is>
-          <t>LTU</t>
-        </is>
-      </c>
-      <c r="C680" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D680" t="n">
-        <v>1.00470685204867</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" s="1" t="n">
-        <v>2263</v>
-      </c>
-      <c r="B681" t="inlineStr">
-        <is>
-          <t>LUX</t>
-        </is>
-      </c>
-      <c r="C681" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D681" t="n">
-        <v>0.345531988873435</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" s="1" t="n">
-        <v>2264</v>
-      </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>LVA</t>
-        </is>
-      </c>
-      <c r="C682" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D682" t="n">
-        <v>1.46175456089919</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" s="1" t="n">
-        <v>2267</v>
-      </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>MAR</t>
-        </is>
-      </c>
-      <c r="C683" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D683" t="n">
-        <v>7.96111730498483</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" s="1" t="n">
-        <v>2273</v>
-      </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>MEX</t>
-        </is>
-      </c>
-      <c r="C684" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D684" t="n">
-        <v>17.1966048280522</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" s="1" t="n">
-        <v>2278</v>
-      </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>MLT</t>
-        </is>
-      </c>
-      <c r="C685" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D685" t="n">
-        <v>2.8480038315487</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" s="1" t="n">
-        <v>2279</v>
-      </c>
-      <c r="B686" t="inlineStr">
-        <is>
-          <t>MMR</t>
-        </is>
-      </c>
-      <c r="C686" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D686" t="inlineStr"/>
-    </row>
-    <row r="687">
-      <c r="A687" s="1" t="n">
-        <v>2288</v>
-      </c>
-      <c r="B687" t="inlineStr">
-        <is>
-          <t>MYS</t>
-        </is>
-      </c>
-      <c r="C687" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D687" t="n">
-        <v>14.020107638443</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" s="1" t="n">
-        <v>2293</v>
-      </c>
-      <c r="B688" t="inlineStr">
-        <is>
-          <t>NGA</t>
-        </is>
-      </c>
-      <c r="C688" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D688" t="inlineStr"/>
-    </row>
-    <row r="689">
-      <c r="A689" s="1" t="n">
-        <v>2295</v>
-      </c>
-      <c r="B689" t="inlineStr">
-        <is>
-          <t>NLD</t>
-        </is>
-      </c>
-      <c r="C689" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D689" t="n">
-        <v>1.30958937641515</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" s="1" t="n">
-        <v>2296</v>
-      </c>
-      <c r="B690" t="inlineStr">
-        <is>
-          <t>NOR</t>
-        </is>
-      </c>
-      <c r="C690" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D690" t="n">
-        <v>0.456615208184397</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" s="1" t="n">
-        <v>2299</v>
-      </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>NZL</t>
-        </is>
-      </c>
-      <c r="C691" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D691" t="n">
-        <v>3.2038226492858</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" s="1" t="n">
-        <v>2303</v>
-      </c>
-      <c r="B692" t="inlineStr">
-        <is>
-          <t>PAK</t>
-        </is>
-      </c>
-      <c r="C692" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D692" t="inlineStr"/>
-    </row>
-    <row r="693">
-      <c r="A693" s="1" t="n">
-        <v>2305</v>
-      </c>
-      <c r="B693" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="C693" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D693" t="inlineStr"/>
-    </row>
-    <row r="694">
-      <c r="A694" s="1" t="n">
-        <v>2306</v>
-      </c>
-      <c r="B694" t="inlineStr">
-        <is>
-          <t>PHL</t>
-        </is>
-      </c>
-      <c r="C694" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D694" t="n">
-        <v>14.1895600248204</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" s="1" t="n">
-        <v>2309</v>
-      </c>
-      <c r="B695" t="inlineStr">
-        <is>
-          <t>POL</t>
-        </is>
-      </c>
-      <c r="C695" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D695" t="n">
-        <v>4.05151988034782</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" s="1" t="n">
-        <v>2313</v>
-      </c>
-      <c r="B696" t="inlineStr">
-        <is>
-          <t>PRT</t>
-        </is>
-      </c>
-      <c r="C696" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D696" t="n">
-        <v>4.95387039532298</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" s="1" t="n">
-        <v>2320</v>
-      </c>
-      <c r="B697" t="inlineStr">
-        <is>
-          <t>ROU</t>
-        </is>
-      </c>
-      <c r="C697" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D697" t="n">
-        <v>4.52784666028597</v>
-      </c>
-    </row>
-    <row r="698">
-      <c r="A698" s="1" t="n">
-        <v>2321</v>
-      </c>
-      <c r="B698" t="inlineStr">
-        <is>
-          <t>RUS</t>
-        </is>
-      </c>
-      <c r="C698" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D698" t="inlineStr"/>
-    </row>
-    <row r="699">
-      <c r="A699" s="1" t="n">
-        <v>2324</v>
-      </c>
-      <c r="B699" t="inlineStr">
-        <is>
-          <t>SAU</t>
-        </is>
-      </c>
-      <c r="C699" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D699" t="n">
-        <v>2.39041526354088</v>
-      </c>
-    </row>
-    <row r="700">
-      <c r="A700" s="1" t="n">
-        <v>2326</v>
-      </c>
-      <c r="B700" t="inlineStr">
-        <is>
-          <t>SEN</t>
-        </is>
-      </c>
-      <c r="C700" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D700" t="n">
-        <v>9.86295387445667</v>
-      </c>
-    </row>
-    <row r="701">
-      <c r="A701" s="1" t="n">
-        <v>2327</v>
-      </c>
-      <c r="B701" t="inlineStr">
-        <is>
-          <t>SGP</t>
-        </is>
-      </c>
-      <c r="C701" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D701" t="n">
-        <v>0.423379410650531</v>
-      </c>
-    </row>
-    <row r="702">
-      <c r="A702" s="1" t="n">
-        <v>2338</v>
-      </c>
-      <c r="B702" t="inlineStr">
-        <is>
-          <t>STP</t>
-        </is>
-      </c>
-      <c r="C702" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D702" t="inlineStr"/>
-    </row>
-    <row r="703">
-      <c r="A703" s="1" t="n">
-        <v>2340</v>
-      </c>
-      <c r="B703" t="inlineStr">
-        <is>
-          <t>SVK</t>
-        </is>
-      </c>
-      <c r="C703" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D703" t="n">
-        <v>2.69872629068166</v>
-      </c>
-    </row>
-    <row r="704">
-      <c r="A704" s="1" t="n">
-        <v>2341</v>
-      </c>
-      <c r="B704" t="inlineStr">
-        <is>
-          <t>SVN</t>
-        </is>
-      </c>
-      <c r="C704" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D704" t="n">
-        <v>2.6268832941425</v>
-      </c>
-    </row>
-    <row r="705">
-      <c r="A705" s="1" t="n">
-        <v>2342</v>
-      </c>
-      <c r="B705" t="inlineStr">
-        <is>
-          <t>SWE</t>
-        </is>
-      </c>
-      <c r="C705" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D705" t="n">
-        <v>1.29388501735187</v>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" s="1" t="n">
-        <v>2352</v>
-      </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="C706" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D706" t="n">
-        <v>6.75505455085063</v>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" s="1" t="n">
-        <v>2362</v>
-      </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>TUN</t>
-        </is>
-      </c>
-      <c r="C707" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D707" t="inlineStr"/>
-    </row>
-    <row r="708">
-      <c r="A708" s="1" t="n">
-        <v>2363</v>
-      </c>
-      <c r="B708" t="inlineStr">
-        <is>
-          <t>TUR</t>
-        </is>
-      </c>
-      <c r="C708" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D708" t="n">
-        <v>15.4826696359583</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" s="1" t="n">
-        <v>2367</v>
-      </c>
-      <c r="B709" t="inlineStr">
-        <is>
-          <t>UKR</t>
-        </is>
-      </c>
-      <c r="C709" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D709" t="n">
-        <v>7.25891657503026</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" s="1" t="n">
-        <v>2370</v>
-      </c>
-      <c r="B710" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C710" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D710" t="n">
-        <v>13.418892172087</v>
-      </c>
-    </row>
-    <row r="711">
-      <c r="A711" s="1" t="n">
-        <v>2376</v>
-      </c>
-      <c r="B711" t="inlineStr">
-        <is>
-          <t>VNM</t>
-        </is>
-      </c>
-      <c r="C711" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D711" t="inlineStr"/>
-    </row>
-    <row r="712">
-      <c r="A712" s="1" t="n">
-        <v>2382</v>
-      </c>
-      <c r="B712" t="inlineStr">
-        <is>
-          <t>ZAF</t>
-        </is>
-      </c>
-      <c r="C712" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D712" t="n">
-        <v>15.9129870924546</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
